--- a/artfynd/A 59482-2025 artfynd.xlsx
+++ b/artfynd/A 59482-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68349396</v>
+        <v>68349393</v>
       </c>
       <c r="B2" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549650.8421014447</v>
+        <v>549390</v>
       </c>
       <c r="R2" t="n">
-        <v>7238278.984860668</v>
+        <v>7238231</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2017-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68349404</v>
+        <v>68349397</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549594.8990439161</v>
+        <v>549651</v>
       </c>
       <c r="R3" t="n">
-        <v>7238213.094933437</v>
+        <v>7238279</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2017-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>68349390</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549531.1829073464</v>
+        <v>549531</v>
       </c>
       <c r="R4" t="n">
-        <v>7238235.068621832</v>
+        <v>7238235</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +937,9 @@
           <t>2017-11-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68349425</v>
+        <v>68349396</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,39 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skansnäsån, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549668.1923341057</v>
+        <v>549651</v>
       </c>
       <c r="R5" t="n">
-        <v>7238270.059180577</v>
+        <v>7238279</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,19 +1034,9 @@
           <t>2017-11-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68349397</v>
+        <v>68349424</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,34 +1074,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skansnäsån, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549650.8421014447</v>
+        <v>549644</v>
       </c>
       <c r="R6" t="n">
-        <v>7238278.984860668</v>
+        <v>7238273</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,19 +1136,9 @@
           <t>2017-11-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68349424</v>
+        <v>68349425</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549643.8114025545</v>
+        <v>549668</v>
       </c>
       <c r="R7" t="n">
-        <v>7238273.000185526</v>
+        <v>7238270</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1318,19 +1238,9 @@
           <t>2017-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
